--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$241</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7366" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7525" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1104,6 +1104,21 @@
   </si>
   <si>
     <t>Autre TemplateId</t>
+  </si>
+  <si>
+    <t>Observation.participant.templateId:templateId-other.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.participant.templateId:templateId-other.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Observation.participant.templateId:templateId-other.displayable</t>
+  </si>
+  <si>
+    <t>Observation.participant.templateId:templateId-other.root</t>
+  </si>
+  <si>
+    <t>Observation.participant.templateId:templateId-other.extension</t>
   </si>
   <si>
     <t>Observation.participant.typeCode</t>
@@ -2180,7 +2195,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK236"/>
+  <dimension ref="A1:AK241"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.15234375" customWidth="true" bestFit="true"/>
@@ -13039,26 +13054,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
         <v>354</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E107" s="2"/>
+      <c r="E107" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F107" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>75</v>
@@ -13070,7 +13087,9 @@
         <v>86</v>
       </c>
       <c r="L107" s="2"/>
-      <c r="M107" s="2"/>
+      <c r="M107" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13081,7 +13100,7 @@
         <v>75</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>355</v>
+        <v>75</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>75</v>
@@ -13100,7 +13119,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>356</v>
+        <v>89</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -13118,10 +13137,10 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>357</v>
+        <v>90</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>76</v>
@@ -13138,16 +13157,18 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E108" s="2"/>
+      <c r="E108" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F108" t="s" s="2">
         <v>81</v>
       </c>
@@ -13164,10 +13185,12 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L108" s="2"/>
-      <c r="M108" s="2"/>
+      <c r="M108" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13175,7 +13198,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>359</v>
+        <v>75</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>75</v>
@@ -13193,11 +13216,13 @@
         <v>75</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y108" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z108" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>75</v>
@@ -13215,7 +13240,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>361</v>
+        <v>105</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -13235,16 +13260,18 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E109" s="2"/>
+      <c r="E109" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F109" t="s" s="2">
         <v>81</v>
       </c>
@@ -13261,10 +13288,12 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>294</v>
+        <v>108</v>
       </c>
       <c r="L109" s="2"/>
-      <c r="M109" s="2"/>
+      <c r="M109" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -13314,7 +13343,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>363</v>
+        <v>110</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -13334,18 +13363,20 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E110" s="2"/>
+      <c r="E110" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F110" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>76</v>
@@ -13360,13 +13391,11 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="L110" s="2"/>
       <c r="M110" t="s" s="2">
-        <v>365</v>
+        <v>138</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13417,7 +13446,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>366</v>
+        <v>116</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -13437,17 +13466,17 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="F111" t="s" s="2">
         <v>81</v>
@@ -13465,11 +13494,11 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" t="s" s="2">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -13496,11 +13525,13 @@
         <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -13518,7 +13549,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -13536,12 +13567,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13549,13 +13580,13 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>75</v>
@@ -13564,12 +13595,10 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>369</v>
+        <v>86</v>
       </c>
       <c r="L112" s="2"/>
-      <c r="M112" t="s" s="2">
-        <v>370</v>
-      </c>
+      <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -13580,7 +13609,7 @@
         <v>75</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>75</v>
@@ -13595,13 +13624,11 @@
         <v>75</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>75</v>
+        <v>361</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -13619,10 +13646,10 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>76</v>
@@ -13639,10 +13666,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13668,17 +13695,15 @@
         <v>86</v>
       </c>
       <c r="L113" s="2"/>
-      <c r="M113" t="s" s="2">
-        <v>373</v>
-      </c>
+      <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
-        <v>374</v>
+        <v>75</v>
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>75</v>
@@ -13700,7 +13725,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>75</v>
@@ -13718,7 +13743,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13736,20 +13761,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E114" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>81</v>
       </c>
@@ -13757,7 +13780,7 @@
         <v>76</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>75</v>
@@ -13766,12 +13789,10 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>379</v>
+        <v>294</v>
       </c>
       <c r="L114" s="2"/>
-      <c r="M114" t="s" s="2">
-        <v>380</v>
-      </c>
+      <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13821,7 +13842,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13839,20 +13860,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E115" t="s" s="2">
-        <v>383</v>
-      </c>
+      <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>81</v>
       </c>
@@ -13860,7 +13879,7 @@
         <v>76</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>75</v>
@@ -13869,11 +13888,13 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="L115" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="M115" t="s" s="2">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13924,7 +13945,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13944,17 +13965,17 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>388</v>
+        <v>85</v>
       </c>
       <c r="F116" t="s" s="2">
         <v>81</v>
@@ -13972,11 +13993,11 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>389</v>
+        <v>86</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" t="s" s="2">
-        <v>390</v>
+        <v>87</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14003,13 +14024,11 @@
         <v>75</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>75</v>
@@ -14027,7 +14046,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>391</v>
+        <v>90</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -14045,20 +14064,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E117" t="s" s="2">
-        <v>393</v>
-      </c>
+      <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>81</v>
       </c>
@@ -14066,7 +14083,7 @@
         <v>76</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>75</v>
@@ -14075,11 +14092,11 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14130,7 +14147,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -14150,10 +14167,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14176,14 +14193,16 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>294</v>
+        <v>86</v>
       </c>
       <c r="L118" s="2"/>
-      <c r="M118" s="2"/>
+      <c r="M118" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
-        <v>75</v>
+        <v>379</v>
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
@@ -14205,13 +14224,11 @@
         <v>75</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>75</v>
@@ -14229,7 +14246,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -14249,18 +14266,20 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E119" s="2"/>
+      <c r="E119" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="F119" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>76</v>
@@ -14275,13 +14294,11 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="L119" s="2"/>
       <c r="M119" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14332,10 +14349,10 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>76</v>
@@ -14352,24 +14369,26 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E120" s="2"/>
+      <c r="E120" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="F120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>75</v>
@@ -14378,10 +14397,12 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="L120" s="2"/>
-      <c r="M120" s="2"/>
+      <c r="M120" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -14419,23 +14440,25 @@
         <v>75</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AC120" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD120" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>75</v>
@@ -14449,23 +14472,23 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E121" s="2"/>
+      <c r="E121" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="F121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>75</v>
@@ -14477,10 +14500,12 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="L121" s="2"/>
-      <c r="M121" s="2"/>
+      <c r="M121" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -14530,13 +14555,13 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>75</v>
@@ -14548,19 +14573,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="F122" t="s" s="2">
         <v>81</v>
@@ -14569,7 +14594,7 @@
         <v>76</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>75</v>
@@ -14578,11 +14603,11 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>86</v>
+        <v>384</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" t="s" s="2">
-        <v>87</v>
+        <v>399</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -14609,11 +14634,13 @@
         <v>75</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y122" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z122" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>75</v>
@@ -14631,7 +14658,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -14651,10 +14678,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14665,7 +14692,7 @@
         <v>81</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>75</v>
@@ -14677,12 +14704,10 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>92</v>
+        <v>294</v>
       </c>
       <c r="L123" s="2"/>
-      <c r="M123" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -14732,13 +14757,13 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>94</v>
+        <v>402</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>75</v>
@@ -14750,12 +14775,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14763,13 +14788,13 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>75</v>
@@ -14778,11 +14803,13 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L124" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="M124" t="s" s="2">
-        <v>97</v>
+        <v>405</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14833,10 +14860,10 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>98</v>
+        <v>406</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>76</v>
@@ -14845,7 +14872,7 @@
         <v>75</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>75</v>
@@ -14853,26 +14880,24 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E125" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
@@ -14881,12 +14906,10 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>86</v>
+        <v>408</v>
       </c>
       <c r="L125" s="2"/>
-      <c r="M125" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M125" s="2"/>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -14912,35 +14935,35 @@
         <v>75</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>90</v>
+        <v>407</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>75</v>
@@ -14954,23 +14977,23 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C126" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D126" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E126" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>75</v>
@@ -14982,12 +15005,10 @@
         <v>75</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="L126" s="2"/>
-      <c r="M126" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M126" s="2"/>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -15037,13 +15058,13 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>105</v>
+        <v>407</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>75</v>
@@ -15057,17 +15078,17 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="F127" t="s" s="2">
         <v>81</v>
@@ -15085,11 +15106,11 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -15116,13 +15137,11 @@
         <v>75</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>75</v>
@@ -15140,7 +15159,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -15160,23 +15179,21 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E128" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>75</v>
@@ -15188,11 +15205,11 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" t="s" s="2">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -15201,7 +15218,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>75</v>
@@ -15243,13 +15260,13 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>75</v>
@@ -15263,20 +15280,18 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E129" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>76</v>
@@ -15291,11 +15306,11 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -15346,7 +15361,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -15358,7 +15373,7 @@
         <v>75</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>75</v>
@@ -15366,21 +15381,23 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E130" s="2"/>
+      <c r="E130" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>75</v>
@@ -15392,11 +15409,11 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15423,13 +15440,11 @@
         <v>75</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>75</v>
@@ -15447,13 +15462,13 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>75</v>
@@ -15467,18 +15482,20 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E131" s="2"/>
+      <c r="E131" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F131" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>76</v>
@@ -15493,10 +15510,12 @@
         <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L131" s="2"/>
-      <c r="M131" s="2"/>
+      <c r="M131" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -15507,7 +15526,7 @@
         <v>75</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>427</v>
+        <v>75</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>75</v>
@@ -15522,11 +15541,13 @@
         <v>75</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>428</v>
+        <v>75</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>75</v>
@@ -15544,10 +15565,10 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>429</v>
+        <v>105</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>76</v>
@@ -15564,16 +15585,18 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E132" s="2"/>
+      <c r="E132" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F132" t="s" s="2">
         <v>81</v>
       </c>
@@ -15594,7 +15617,7 @@
       </c>
       <c r="L132" s="2"/>
       <c r="M132" t="s" s="2">
-        <v>432</v>
+        <v>109</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -15606,7 +15629,7 @@
         <v>75</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>75</v>
@@ -15645,7 +15668,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15665,18 +15688,20 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E133" s="2"/>
+      <c r="E133" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F133" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>76</v>
@@ -15691,20 +15716,20 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>436</v>
+        <v>114</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S133" t="s" s="2">
         <v>75</v>
@@ -15746,7 +15771,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -15766,18 +15791,20 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E134" s="2"/>
+      <c r="E134" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="F134" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>76</v>
@@ -15792,10 +15819,12 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L134" s="2"/>
-      <c r="M134" s="2"/>
+      <c r="M134" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -15845,7 +15874,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>441</v>
+        <v>120</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -15865,10 +15894,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15879,7 +15908,7 @@
         <v>81</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>75</v>
@@ -15891,10 +15920,12 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>444</v>
+        <v>96</v>
       </c>
       <c r="L135" s="2"/>
-      <c r="M135" s="2"/>
+      <c r="M135" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -15944,13 +15975,13 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>445</v>
+        <v>126</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>75</v>
@@ -15964,10 +15995,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15975,7 +16006,7 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>76</v>
@@ -15990,7 +16021,7 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>448</v>
+        <v>86</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -16004,7 +16035,7 @@
         <v>75</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>75</v>
+        <v>432</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>75</v>
@@ -16019,13 +16050,11 @@
         <v>75</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>75</v>
+        <v>433</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>75</v>
@@ -16043,10 +16072,10 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>76</v>
@@ -16063,10 +16092,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16089,10 +16118,12 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>452</v>
+        <v>108</v>
       </c>
       <c r="L137" s="2"/>
-      <c r="M137" s="2"/>
+      <c r="M137" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -16103,7 +16134,7 @@
         <v>75</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>75</v>
@@ -16142,7 +16173,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -16162,10 +16193,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16188,14 +16219,16 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>456</v>
+        <v>108</v>
       </c>
       <c r="L138" s="2"/>
-      <c r="M138" s="2"/>
+      <c r="M138" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
-        <v>75</v>
+        <v>442</v>
       </c>
       <c r="Q138" s="2"/>
       <c r="R138" t="s" s="2">
@@ -16241,7 +16274,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -16261,10 +16294,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16287,7 +16320,7 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>460</v>
+        <v>108</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -16340,7 +16373,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -16360,10 +16393,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16386,7 +16419,7 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16439,7 +16472,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -16459,10 +16492,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16485,7 +16518,7 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16538,7 +16571,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -16558,10 +16591,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16584,7 +16617,7 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16637,7 +16670,7 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -16657,10 +16690,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16683,7 +16716,7 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16736,7 +16769,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -16756,10 +16789,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16782,7 +16815,7 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16835,7 +16868,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -16855,10 +16888,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16881,7 +16914,7 @@
         <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16934,7 +16967,7 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -16954,14 +16987,12 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C146" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
         <v>75</v>
       </c>
@@ -16982,11 +17013,9 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="L146" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="L146" s="2"/>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -17037,13 +17066,13 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>402</v>
+        <v>474</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>75</v>
@@ -17057,18 +17086,16 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>408</v>
+        <v>476</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E147" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>81</v>
       </c>
@@ -17085,12 +17112,10 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>86</v>
+        <v>477</v>
       </c>
       <c r="L147" s="2"/>
-      <c r="M147" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M147" s="2"/>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -17116,11 +17141,13 @@
         <v>75</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y147" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z147" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>75</v>
@@ -17138,7 +17165,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>90</v>
+        <v>478</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -17158,10 +17185,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>410</v>
+        <v>480</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17172,7 +17199,7 @@
         <v>81</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>75</v>
@@ -17184,12 +17211,10 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>92</v>
+        <v>481</v>
       </c>
       <c r="L148" s="2"/>
-      <c r="M148" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M148" s="2"/>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -17239,13 +17264,13 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>94</v>
+        <v>482</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>75</v>
@@ -17259,10 +17284,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>412</v>
+        <v>484</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17285,12 +17310,10 @@
         <v>75</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>96</v>
+        <v>485</v>
       </c>
       <c r="L149" s="2"/>
-      <c r="M149" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M149" s="2"/>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -17340,7 +17363,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>98</v>
+        <v>486</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -17352,7 +17375,7 @@
         <v>75</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>75</v>
@@ -17360,18 +17383,16 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>414</v>
+        <v>488</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E150" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>81</v>
       </c>
@@ -17388,12 +17409,10 @@
         <v>75</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>86</v>
+        <v>489</v>
       </c>
       <c r="L150" s="2"/>
-      <c r="M150" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M150" s="2"/>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -17419,11 +17438,13 @@
         <v>75</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y150" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z150" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>75</v>
@@ -17441,7 +17462,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>90</v>
+        <v>490</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -17461,40 +17482,40 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C151" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="D151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="B151" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E151" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L151" s="2"/>
-      <c r="M151" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M151" s="2"/>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -17544,13 +17565,13 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>105</v>
+        <v>407</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>75</v>
@@ -17567,14 +17588,14 @@
         <v>494</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="F152" t="s" s="2">
         <v>81</v>
@@ -17592,11 +17613,11 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17623,13 +17644,11 @@
         <v>75</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>75</v>
@@ -17647,7 +17666,7 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -17670,20 +17689,18 @@
         <v>495</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E153" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>75</v>
@@ -17695,11 +17712,11 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" t="s" s="2">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17708,7 +17725,7 @@
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>75</v>
@@ -17750,13 +17767,13 @@
         <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>75</v>
@@ -17773,17 +17790,15 @@
         <v>496</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E154" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G154" t="s" s="2">
         <v>76</v>
@@ -17798,11 +17813,11 @@
         <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -17853,7 +17868,7 @@
         <v>75</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -17865,7 +17880,7 @@
         <v>75</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>75</v>
@@ -17876,18 +17891,20 @@
         <v>497</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E155" s="2"/>
+      <c r="E155" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>75</v>
@@ -17899,11 +17916,11 @@
         <v>75</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" t="s" s="2">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -17930,13 +17947,11 @@
         <v>75</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>75</v>
@@ -17954,13 +17969,13 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>75</v>
@@ -17977,15 +17992,17 @@
         <v>498</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E156" s="2"/>
+      <c r="E156" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F156" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G156" t="s" s="2">
         <v>76</v>
@@ -18000,10 +18017,12 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L156" s="2"/>
-      <c r="M156" s="2"/>
+      <c r="M156" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -18014,7 +18033,7 @@
         <v>75</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>427</v>
+        <v>75</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>75</v>
@@ -18029,11 +18048,13 @@
         <v>75</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y156" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z156" t="s" s="2">
-        <v>428</v>
+        <v>75</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>75</v>
@@ -18051,10 +18072,10 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>429</v>
+        <v>105</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>76</v>
@@ -18074,13 +18095,15 @@
         <v>499</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E157" s="2"/>
+      <c r="E157" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F157" t="s" s="2">
         <v>81</v>
       </c>
@@ -18101,7 +18124,7 @@
       </c>
       <c r="L157" s="2"/>
       <c r="M157" t="s" s="2">
-        <v>432</v>
+        <v>109</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -18113,7 +18136,7 @@
         <v>75</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>75</v>
@@ -18152,7 +18175,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -18175,15 +18198,17 @@
         <v>500</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E158" s="2"/>
+      <c r="E158" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F158" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>76</v>
@@ -18198,20 +18223,20 @@
         <v>75</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" t="s" s="2">
-        <v>436</v>
+        <v>114</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="Q158" s="2"/>
       <c r="R158" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S158" t="s" s="2">
         <v>75</v>
@@ -18253,7 +18278,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -18276,15 +18301,17 @@
         <v>501</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E159" s="2"/>
+      <c r="E159" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="F159" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>76</v>
@@ -18299,10 +18326,12 @@
         <v>75</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L159" s="2"/>
-      <c r="M159" s="2"/>
+      <c r="M159" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -18352,7 +18381,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>441</v>
+        <v>120</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -18375,7 +18404,7 @@
         <v>502</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18386,7 +18415,7 @@
         <v>81</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>75</v>
@@ -18398,10 +18427,12 @@
         <v>75</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>444</v>
+        <v>96</v>
       </c>
       <c r="L160" s="2"/>
-      <c r="M160" s="2"/>
+      <c r="M160" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -18451,13 +18482,13 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>445</v>
+        <v>126</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>75</v>
@@ -18474,7 +18505,7 @@
         <v>503</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18482,7 +18513,7 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>76</v>
@@ -18497,7 +18528,7 @@
         <v>75</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>448</v>
+        <v>86</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18511,7 +18542,7 @@
         <v>75</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>75</v>
+        <v>432</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>75</v>
@@ -18526,13 +18557,11 @@
         <v>75</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>75</v>
+        <v>433</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>75</v>
@@ -18550,10 +18579,10 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>76</v>
@@ -18573,7 +18602,7 @@
         <v>504</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18596,10 +18625,12 @@
         <v>75</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>452</v>
+        <v>108</v>
       </c>
       <c r="L162" s="2"/>
-      <c r="M162" s="2"/>
+      <c r="M162" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -18610,7 +18641,7 @@
         <v>75</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>75</v>
@@ -18649,7 +18680,7 @@
         <v>75</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -18672,7 +18703,7 @@
         <v>505</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18695,14 +18726,16 @@
         <v>75</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>456</v>
+        <v>108</v>
       </c>
       <c r="L163" s="2"/>
-      <c r="M163" s="2"/>
+      <c r="M163" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
-        <v>75</v>
+        <v>442</v>
       </c>
       <c r="Q163" s="2"/>
       <c r="R163" t="s" s="2">
@@ -18748,7 +18781,7 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -18771,7 +18804,7 @@
         <v>506</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18794,7 +18827,7 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>507</v>
+        <v>108</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18847,7 +18880,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -18867,10 +18900,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18893,7 +18926,7 @@
         <v>75</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18946,7 +18979,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -18966,10 +18999,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18992,7 +19025,7 @@
         <v>75</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -19045,7 +19078,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -19065,10 +19098,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19091,7 +19124,7 @@
         <v>75</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -19144,7 +19177,7 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -19164,10 +19197,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19190,7 +19223,7 @@
         <v>75</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -19243,7 +19276,7 @@
         <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -19263,10 +19296,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19289,7 +19322,7 @@
         <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -19342,7 +19375,7 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -19365,7 +19398,7 @@
         <v>513</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19388,7 +19421,7 @@
         <v>75</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19441,7 +19474,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19464,11 +19497,9 @@
         <v>514</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C171" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
         <v>75</v>
       </c>
@@ -19477,7 +19508,7 @@
         <v>81</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>75</v>
@@ -19489,11 +19520,9 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="L171" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="L171" s="2"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -19544,13 +19573,13 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>402</v>
+        <v>474</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>75</v>
@@ -19564,18 +19593,16 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>408</v>
+        <v>476</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E172" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
         <v>81</v>
       </c>
@@ -19592,12 +19619,10 @@
         <v>75</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>86</v>
+        <v>477</v>
       </c>
       <c r="L172" s="2"/>
-      <c r="M172" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M172" s="2"/>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -19623,11 +19648,13 @@
         <v>75</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y172" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z172" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>75</v>
@@ -19645,7 +19672,7 @@
         <v>75</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>90</v>
+        <v>478</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -19665,10 +19692,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>410</v>
+        <v>480</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19679,7 +19706,7 @@
         <v>81</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>75</v>
@@ -19691,12 +19718,10 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>92</v>
+        <v>481</v>
       </c>
       <c r="L173" s="2"/>
-      <c r="M173" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M173" s="2"/>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -19746,13 +19771,13 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>94</v>
+        <v>482</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>75</v>
@@ -19766,10 +19791,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>412</v>
+        <v>484</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19792,12 +19817,10 @@
         <v>75</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>96</v>
+        <v>485</v>
       </c>
       <c r="L174" s="2"/>
-      <c r="M174" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M174" s="2"/>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -19847,7 +19870,7 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>98</v>
+        <v>486</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -19859,7 +19882,7 @@
         <v>75</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>75</v>
@@ -19867,18 +19890,16 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>414</v>
+        <v>488</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E175" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>81</v>
       </c>
@@ -19895,12 +19916,10 @@
         <v>75</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>86</v>
+        <v>489</v>
       </c>
       <c r="L175" s="2"/>
-      <c r="M175" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -19926,11 +19945,13 @@
         <v>75</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y175" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z175" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>75</v>
@@ -19948,7 +19969,7 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>90</v>
+        <v>490</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -19968,40 +19989,40 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C176" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="D176" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="B176" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C176" s="2"/>
-      <c r="D176" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E176" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G176" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H176" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I176" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J176" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K176" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L176" s="2"/>
-      <c r="M176" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M176" s="2"/>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -20051,13 +20072,13 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>105</v>
+        <v>407</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>75</v>
@@ -20074,14 +20095,14 @@
         <v>522</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E177" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="F177" t="s" s="2">
         <v>81</v>
@@ -20099,11 +20120,11 @@
         <v>75</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -20130,13 +20151,11 @@
         <v>75</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y177" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y177" s="2"/>
       <c r="Z177" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>75</v>
@@ -20154,7 +20173,7 @@
         <v>75</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -20177,20 +20196,18 @@
         <v>523</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E178" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>75</v>
@@ -20202,11 +20219,11 @@
         <v>75</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" t="s" s="2">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -20215,7 +20232,7 @@
       </c>
       <c r="Q178" s="2"/>
       <c r="R178" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S178" t="s" s="2">
         <v>75</v>
@@ -20257,13 +20274,13 @@
         <v>75</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>75</v>
@@ -20280,17 +20297,15 @@
         <v>524</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E179" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G179" t="s" s="2">
         <v>76</v>
@@ -20305,11 +20320,11 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -20360,7 +20375,7 @@
         <v>75</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -20372,7 +20387,7 @@
         <v>75</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>75</v>
@@ -20383,18 +20398,20 @@
         <v>525</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E180" s="2"/>
+      <c r="E180" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>75</v>
@@ -20406,11 +20423,11 @@
         <v>75</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" t="s" s="2">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -20437,13 +20454,11 @@
         <v>75</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>75</v>
@@ -20461,13 +20476,13 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>75</v>
@@ -20484,15 +20499,17 @@
         <v>526</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E181" s="2"/>
+      <c r="E181" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F181" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G181" t="s" s="2">
         <v>76</v>
@@ -20507,10 +20524,12 @@
         <v>75</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L181" s="2"/>
-      <c r="M181" s="2"/>
+      <c r="M181" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -20521,7 +20540,7 @@
         <v>75</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>527</v>
+        <v>75</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>75</v>
@@ -20536,11 +20555,13 @@
         <v>75</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y181" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y181" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z181" t="s" s="2">
-        <v>428</v>
+        <v>75</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>75</v>
@@ -20558,10 +20579,10 @@
         <v>75</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>429</v>
+        <v>105</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>76</v>
@@ -20578,16 +20599,18 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E182" s="2"/>
+      <c r="E182" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F182" t="s" s="2">
         <v>81</v>
       </c>
@@ -20608,7 +20631,7 @@
       </c>
       <c r="L182" s="2"/>
       <c r="M182" t="s" s="2">
-        <v>432</v>
+        <v>109</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -20620,7 +20643,7 @@
         <v>75</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>75</v>
@@ -20659,7 +20682,7 @@
         <v>75</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -20679,18 +20702,20 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E183" s="2"/>
+      <c r="E183" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F183" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>76</v>
@@ -20705,20 +20730,20 @@
         <v>75</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" t="s" s="2">
-        <v>436</v>
+        <v>114</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="Q183" s="2"/>
       <c r="R183" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S183" t="s" s="2">
         <v>75</v>
@@ -20760,7 +20785,7 @@
         <v>75</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -20780,18 +20805,20 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E184" s="2"/>
+      <c r="E184" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="F184" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G184" t="s" s="2">
         <v>76</v>
@@ -20806,10 +20833,12 @@
         <v>75</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L184" s="2"/>
-      <c r="M184" s="2"/>
+      <c r="M184" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -20859,7 +20888,7 @@
         <v>75</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>441</v>
+        <v>120</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -20879,10 +20908,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20893,7 +20922,7 @@
         <v>81</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>75</v>
@@ -20905,10 +20934,12 @@
         <v>75</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>444</v>
+        <v>96</v>
       </c>
       <c r="L185" s="2"/>
-      <c r="M185" s="2"/>
+      <c r="M185" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -20958,13 +20989,13 @@
         <v>75</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>445</v>
+        <v>126</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI185" t="s" s="2">
         <v>75</v>
@@ -20978,10 +21009,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20989,7 +21020,7 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G186" t="s" s="2">
         <v>76</v>
@@ -21004,7 +21035,7 @@
         <v>75</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>448</v>
+        <v>86</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -21018,7 +21049,7 @@
         <v>75</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>75</v>
+        <v>532</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>75</v>
@@ -21033,13 +21064,11 @@
         <v>75</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y186" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>75</v>
+        <v>433</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>75</v>
@@ -21057,10 +21086,10 @@
         <v>75</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>76</v>
@@ -21080,7 +21109,7 @@
         <v>533</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21103,10 +21132,12 @@
         <v>75</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>534</v>
+        <v>108</v>
       </c>
       <c r="L187" s="2"/>
-      <c r="M187" s="2"/>
+      <c r="M187" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -21117,7 +21148,7 @@
         <v>75</v>
       </c>
       <c r="S187" t="s" s="2">
-        <v>75</v>
+        <v>442</v>
       </c>
       <c r="T187" t="s" s="2">
         <v>75</v>
@@ -21156,7 +21187,7 @@
         <v>75</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -21176,10 +21207,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21202,14 +21233,16 @@
         <v>75</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>456</v>
+        <v>108</v>
       </c>
       <c r="L188" s="2"/>
-      <c r="M188" s="2"/>
+      <c r="M188" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
-        <v>75</v>
+        <v>442</v>
       </c>
       <c r="Q188" s="2"/>
       <c r="R188" t="s" s="2">
@@ -21255,7 +21288,7 @@
         <v>75</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -21275,10 +21308,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21301,7 +21334,7 @@
         <v>75</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>537</v>
+        <v>108</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -21354,7 +21387,7 @@
         <v>75</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -21374,10 +21407,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21400,7 +21433,7 @@
         <v>75</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
@@ -21453,7 +21486,7 @@
         <v>75</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -21473,10 +21506,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21499,7 +21532,7 @@
         <v>75</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
@@ -21552,7 +21585,7 @@
         <v>75</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -21572,10 +21605,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21598,7 +21631,7 @@
         <v>75</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>472</v>
+        <v>539</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -21651,7 +21684,7 @@
         <v>75</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -21671,10 +21704,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21697,7 +21730,7 @@
         <v>75</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
@@ -21750,7 +21783,7 @@
         <v>75</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -21770,10 +21803,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21796,7 +21829,7 @@
         <v>75</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>480</v>
+        <v>542</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -21849,7 +21882,7 @@
         <v>75</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -21872,7 +21905,7 @@
         <v>543</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21895,7 +21928,7 @@
         <v>75</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -21948,7 +21981,7 @@
         <v>75</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -21971,11 +22004,9 @@
         <v>544</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C196" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
         <v>75</v>
       </c>
@@ -21984,7 +22015,7 @@
         <v>81</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>75</v>
@@ -21996,11 +22027,9 @@
         <v>75</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="L196" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="L196" s="2"/>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -22051,13 +22080,13 @@
         <v>75</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>402</v>
+        <v>474</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>75</v>
@@ -22071,18 +22100,16 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>408</v>
+        <v>476</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E197" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
         <v>81</v>
       </c>
@@ -22099,12 +22126,10 @@
         <v>75</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>86</v>
+        <v>477</v>
       </c>
       <c r="L197" s="2"/>
-      <c r="M197" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M197" s="2"/>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -22130,11 +22155,13 @@
         <v>75</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y197" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y197" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z197" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>75</v>
@@ -22152,7 +22179,7 @@
         <v>75</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>90</v>
+        <v>478</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -22172,10 +22199,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>410</v>
+        <v>480</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22186,7 +22213,7 @@
         <v>81</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H198" t="s" s="2">
         <v>75</v>
@@ -22198,12 +22225,10 @@
         <v>75</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>92</v>
+        <v>481</v>
       </c>
       <c r="L198" s="2"/>
-      <c r="M198" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M198" s="2"/>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -22253,13 +22278,13 @@
         <v>75</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>94</v>
+        <v>482</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI198" t="s" s="2">
         <v>75</v>
@@ -22273,10 +22298,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>412</v>
+        <v>484</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22299,12 +22324,10 @@
         <v>75</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>96</v>
+        <v>485</v>
       </c>
       <c r="L199" s="2"/>
-      <c r="M199" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M199" s="2"/>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -22354,7 +22377,7 @@
         <v>75</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>98</v>
+        <v>486</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -22366,7 +22389,7 @@
         <v>75</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>75</v>
@@ -22374,18 +22397,16 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>414</v>
+        <v>488</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E200" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
         <v>81</v>
       </c>
@@ -22402,12 +22423,10 @@
         <v>75</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>86</v>
+        <v>489</v>
       </c>
       <c r="L200" s="2"/>
-      <c r="M200" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M200" s="2"/>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -22433,11 +22452,13 @@
         <v>75</v>
       </c>
       <c r="X200" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y200" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y200" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z200" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>75</v>
@@ -22455,7 +22476,7 @@
         <v>75</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>90</v>
+        <v>490</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
@@ -22475,40 +22496,40 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="D201" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E201" s="2"/>
+      <c r="F201" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H201" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I201" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J201" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K201" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L201" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="B201" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C201" s="2"/>
-      <c r="D201" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E201" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F201" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G201" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H201" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I201" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J201" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K201" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L201" s="2"/>
-      <c r="M201" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M201" s="2"/>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -22558,13 +22579,13 @@
         <v>75</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>105</v>
+        <v>407</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI201" t="s" s="2">
         <v>75</v>
@@ -22581,14 +22602,14 @@
         <v>552</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E202" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="F202" t="s" s="2">
         <v>81</v>
@@ -22606,11 +22627,11 @@
         <v>75</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -22637,13 +22658,11 @@
         <v>75</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y202" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y202" s="2"/>
       <c r="Z202" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>75</v>
@@ -22661,7 +22680,7 @@
         <v>75</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -22684,20 +22703,18 @@
         <v>553</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E203" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G203" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H203" t="s" s="2">
         <v>75</v>
@@ -22709,11 +22726,11 @@
         <v>75</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" t="s" s="2">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -22722,7 +22739,7 @@
       </c>
       <c r="Q203" s="2"/>
       <c r="R203" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S203" t="s" s="2">
         <v>75</v>
@@ -22764,13 +22781,13 @@
         <v>75</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI203" t="s" s="2">
         <v>75</v>
@@ -22787,17 +22804,15 @@
         <v>554</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E204" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G204" t="s" s="2">
         <v>76</v>
@@ -22812,11 +22827,11 @@
         <v>75</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -22867,7 +22882,7 @@
         <v>75</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -22879,7 +22894,7 @@
         <v>75</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>75</v>
@@ -22890,18 +22905,20 @@
         <v>555</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E205" s="2"/>
+      <c r="E205" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F205" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>75</v>
@@ -22913,11 +22930,11 @@
         <v>75</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" t="s" s="2">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -22944,13 +22961,11 @@
         <v>75</v>
       </c>
       <c r="X205" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y205" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y205" s="2"/>
       <c r="Z205" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA205" t="s" s="2">
         <v>75</v>
@@ -22968,13 +22983,13 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI205" t="s" s="2">
         <v>75</v>
@@ -22991,15 +23006,17 @@
         <v>556</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E206" s="2"/>
+      <c r="E206" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F206" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G206" t="s" s="2">
         <v>76</v>
@@ -23014,10 +23031,12 @@
         <v>75</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L206" s="2"/>
-      <c r="M206" s="2"/>
+      <c r="M206" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -23028,7 +23047,7 @@
         <v>75</v>
       </c>
       <c r="S206" t="s" s="2">
-        <v>557</v>
+        <v>75</v>
       </c>
       <c r="T206" t="s" s="2">
         <v>75</v>
@@ -23043,11 +23062,13 @@
         <v>75</v>
       </c>
       <c r="X206" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y206" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y206" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z206" t="s" s="2">
-        <v>428</v>
+        <v>75</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>75</v>
@@ -23065,10 +23086,10 @@
         <v>75</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>429</v>
+        <v>105</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>76</v>
@@ -23085,16 +23106,18 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E207" s="2"/>
+      <c r="E207" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F207" t="s" s="2">
         <v>81</v>
       </c>
@@ -23115,7 +23138,7 @@
       </c>
       <c r="L207" s="2"/>
       <c r="M207" t="s" s="2">
-        <v>432</v>
+        <v>109</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -23127,7 +23150,7 @@
         <v>75</v>
       </c>
       <c r="S207" t="s" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="T207" t="s" s="2">
         <v>75</v>
@@ -23166,7 +23189,7 @@
         <v>75</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -23186,18 +23209,20 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E208" s="2"/>
+      <c r="E208" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F208" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G208" t="s" s="2">
         <v>76</v>
@@ -23212,20 +23237,20 @@
         <v>75</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L208" s="2"/>
       <c r="M208" t="s" s="2">
-        <v>436</v>
+        <v>114</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="Q208" s="2"/>
       <c r="R208" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S208" t="s" s="2">
         <v>75</v>
@@ -23267,7 +23292,7 @@
         <v>75</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -23287,18 +23312,20 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E209" s="2"/>
+      <c r="E209" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="F209" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G209" t="s" s="2">
         <v>76</v>
@@ -23313,10 +23340,12 @@
         <v>75</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L209" s="2"/>
-      <c r="M209" s="2"/>
+      <c r="M209" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
@@ -23366,7 +23395,7 @@
         <v>75</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>441</v>
+        <v>120</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -23386,10 +23415,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23400,7 +23429,7 @@
         <v>81</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>75</v>
@@ -23412,10 +23441,12 @@
         <v>75</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>444</v>
+        <v>96</v>
       </c>
       <c r="L210" s="2"/>
-      <c r="M210" s="2"/>
+      <c r="M210" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -23465,13 +23496,13 @@
         <v>75</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>445</v>
+        <v>126</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>75</v>
@@ -23485,10 +23516,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23496,7 +23527,7 @@
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G211" t="s" s="2">
         <v>76</v>
@@ -23511,7 +23542,7 @@
         <v>75</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>448</v>
+        <v>86</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -23525,7 +23556,7 @@
         <v>75</v>
       </c>
       <c r="S211" t="s" s="2">
-        <v>75</v>
+        <v>562</v>
       </c>
       <c r="T211" t="s" s="2">
         <v>75</v>
@@ -23540,13 +23571,11 @@
         <v>75</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y211" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>75</v>
+        <v>433</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>75</v>
@@ -23564,10 +23593,10 @@
         <v>75</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH211" t="s" s="2">
         <v>76</v>
@@ -23587,7 +23616,7 @@
         <v>563</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23610,10 +23639,12 @@
         <v>75</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>564</v>
+        <v>108</v>
       </c>
       <c r="L212" s="2"/>
-      <c r="M212" s="2"/>
+      <c r="M212" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -23624,7 +23655,7 @@
         <v>75</v>
       </c>
       <c r="S212" t="s" s="2">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="T212" t="s" s="2">
         <v>75</v>
@@ -23663,7 +23694,7 @@
         <v>75</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
@@ -23683,10 +23714,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23709,14 +23740,16 @@
         <v>75</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>456</v>
+        <v>108</v>
       </c>
       <c r="L213" s="2"/>
-      <c r="M213" s="2"/>
+      <c r="M213" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
-        <v>75</v>
+        <v>442</v>
       </c>
       <c r="Q213" s="2"/>
       <c r="R213" t="s" s="2">
@@ -23762,7 +23795,7 @@
         <v>75</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -23782,10 +23815,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23808,7 +23841,7 @@
         <v>75</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>537</v>
+        <v>108</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -23861,7 +23894,7 @@
         <v>75</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -23881,10 +23914,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -23907,7 +23940,7 @@
         <v>75</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
@@ -23960,7 +23993,7 @@
         <v>75</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -23980,10 +24013,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24006,7 +24039,7 @@
         <v>75</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
@@ -24059,7 +24092,7 @@
         <v>75</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -24079,10 +24112,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24105,7 +24138,7 @@
         <v>75</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>472</v>
+        <v>569</v>
       </c>
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
@@ -24158,7 +24191,7 @@
         <v>75</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -24181,7 +24214,7 @@
         <v>570</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24204,7 +24237,7 @@
         <v>75</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
@@ -24257,7 +24290,7 @@
         <v>75</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -24280,7 +24313,7 @@
         <v>571</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24303,7 +24336,7 @@
         <v>75</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>480</v>
+        <v>542</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -24356,7 +24389,7 @@
         <v>75</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -24379,7 +24412,7 @@
         <v>572</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24402,7 +24435,7 @@
         <v>75</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24455,7 +24488,7 @@
         <v>75</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -24478,7 +24511,7 @@
         <v>573</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>573</v>
+        <v>472</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24489,7 +24522,7 @@
         <v>81</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H221" t="s" s="2">
         <v>75</v>
@@ -24501,7 +24534,7 @@
         <v>75</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>574</v>
+        <v>473</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24554,13 +24587,13 @@
         <v>75</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>573</v>
+        <v>474</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI221" t="s" s="2">
         <v>75</v>
@@ -24574,10 +24607,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>575</v>
+        <v>476</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24588,7 +24621,7 @@
         <v>81</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>75</v>
@@ -24600,7 +24633,7 @@
         <v>75</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>576</v>
+        <v>477</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24653,13 +24686,13 @@
         <v>75</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>575</v>
+        <v>478</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI222" t="s" s="2">
         <v>75</v>
@@ -24673,10 +24706,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>577</v>
+        <v>480</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24687,7 +24720,7 @@
         <v>81</v>
       </c>
       <c r="G223" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H223" t="s" s="2">
         <v>75</v>
@@ -24699,7 +24732,7 @@
         <v>75</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>578</v>
+        <v>481</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24752,13 +24785,13 @@
         <v>75</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>577</v>
+        <v>482</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH223" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI223" t="s" s="2">
         <v>75</v>
@@ -24772,10 +24805,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>579</v>
+        <v>484</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24786,7 +24819,7 @@
         <v>81</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>75</v>
@@ -24798,12 +24831,10 @@
         <v>75</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>580</v>
+        <v>485</v>
       </c>
       <c r="L224" s="2"/>
-      <c r="M224" t="s" s="2">
-        <v>581</v>
-      </c>
+      <c r="M224" s="2"/>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
@@ -24853,13 +24884,13 @@
         <v>75</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>579</v>
+        <v>486</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI224" t="s" s="2">
         <v>75</v>
@@ -24873,18 +24904,16 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>582</v>
+        <v>488</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E225" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E225" s="2"/>
       <c r="F225" t="s" s="2">
         <v>81</v>
       </c>
@@ -24901,12 +24930,10 @@
         <v>75</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>86</v>
+        <v>489</v>
       </c>
       <c r="L225" s="2"/>
-      <c r="M225" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M225" s="2"/>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
@@ -24932,11 +24959,13 @@
         <v>75</v>
       </c>
       <c r="X225" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y225" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y225" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z225" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>75</v>
@@ -24954,7 +24983,7 @@
         <v>75</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>90</v>
+        <v>490</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -24974,10 +25003,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25000,12 +25029,10 @@
         <v>75</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>92</v>
+        <v>579</v>
       </c>
       <c r="L226" s="2"/>
-      <c r="M226" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M226" s="2"/>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
@@ -25055,7 +25082,7 @@
         <v>75</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>94</v>
+        <v>578</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -25075,10 +25102,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25089,7 +25116,7 @@
         <v>81</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H227" t="s" s="2">
         <v>75</v>
@@ -25101,12 +25128,10 @@
         <v>75</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>96</v>
+        <v>581</v>
       </c>
       <c r="L227" s="2"/>
-      <c r="M227" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M227" s="2"/>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
@@ -25156,19 +25181,19 @@
         <v>75</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>98</v>
+        <v>580</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH227" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI227" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK227" t="s" s="2">
         <v>75</v>
@@ -25176,23 +25201,21 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E228" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>75</v>
@@ -25204,12 +25227,10 @@
         <v>75</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>86</v>
+        <v>583</v>
       </c>
       <c r="L228" s="2"/>
-      <c r="M228" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M228" s="2"/>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
@@ -25235,11 +25256,13 @@
         <v>75</v>
       </c>
       <c r="X228" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y228" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y228" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z228" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>75</v>
@@ -25257,13 +25280,13 @@
         <v>75</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>90</v>
+        <v>582</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>75</v>
@@ -25277,23 +25300,21 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E229" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>75</v>
@@ -25305,11 +25326,11 @@
         <v>75</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>103</v>
+        <v>585</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" t="s" s="2">
-        <v>104</v>
+        <v>586</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -25360,13 +25381,13 @@
         <v>75</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>105</v>
+        <v>584</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>75</v>
@@ -25390,7 +25411,7 @@
         <v>75</v>
       </c>
       <c r="E230" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="F230" t="s" s="2">
         <v>81</v>
@@ -25408,11 +25429,11 @@
         <v>75</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L230" s="2"/>
       <c r="M230" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -25439,13 +25460,11 @@
         <v>75</v>
       </c>
       <c r="X230" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y230" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y230" s="2"/>
       <c r="Z230" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>75</v>
@@ -25463,7 +25482,7 @@
         <v>75</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -25492,14 +25511,12 @@
       <c r="D231" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E231" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>75</v>
@@ -25511,11 +25528,11 @@
         <v>75</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" t="s" s="2">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -25524,7 +25541,7 @@
       </c>
       <c r="Q231" s="2"/>
       <c r="R231" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S231" t="s" s="2">
         <v>75</v>
@@ -25566,13 +25583,13 @@
         <v>75</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI231" t="s" s="2">
         <v>75</v>
@@ -25595,11 +25612,9 @@
       <c r="D232" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E232" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G232" t="s" s="2">
         <v>76</v>
@@ -25614,11 +25629,11 @@
         <v>75</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L232" s="2"/>
       <c r="M232" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -25669,7 +25684,7 @@
         <v>75</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -25681,7 +25696,7 @@
         <v>75</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK232" t="s" s="2">
         <v>75</v>
@@ -25698,12 +25713,14 @@
       <c r="D233" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E233" s="2"/>
+      <c r="E233" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H233" t="s" s="2">
         <v>75</v>
@@ -25715,11 +25732,11 @@
         <v>75</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L233" s="2"/>
       <c r="M233" t="s" s="2">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -25746,13 +25763,11 @@
         <v>75</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y233" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y233" s="2"/>
       <c r="Z233" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>75</v>
@@ -25770,13 +25785,13 @@
         <v>75</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI233" t="s" s="2">
         <v>75</v>
@@ -25799,7 +25814,9 @@
       <c r="D234" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E234" s="2"/>
+      <c r="E234" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F234" t="s" s="2">
         <v>81</v>
       </c>
@@ -25816,10 +25833,12 @@
         <v>75</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L234" s="2"/>
-      <c r="M234" s="2"/>
+      <c r="M234" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
@@ -25827,7 +25846,7 @@
       </c>
       <c r="Q234" s="2"/>
       <c r="R234" t="s" s="2">
-        <v>592</v>
+        <v>75</v>
       </c>
       <c r="S234" t="s" s="2">
         <v>75</v>
@@ -25845,11 +25864,13 @@
         <v>75</v>
       </c>
       <c r="X234" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y234" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y234" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z234" t="s" s="2">
-        <v>593</v>
+        <v>75</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>75</v>
@@ -25867,7 +25888,7 @@
         <v>75</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>591</v>
+        <v>105</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
@@ -25887,18 +25908,20 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E235" s="2"/>
+      <c r="E235" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="F235" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G235" t="s" s="2">
         <v>76</v>
@@ -25913,10 +25936,12 @@
         <v>75</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>595</v>
+        <v>108</v>
       </c>
       <c r="L235" s="2"/>
-      <c r="M235" s="2"/>
+      <c r="M235" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
@@ -25966,10 +25991,10 @@
         <v>75</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>594</v>
+        <v>110</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>76</v>
@@ -25986,21 +26011,23 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E236" s="2"/>
+      <c r="E236" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="F236" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>75</v>
@@ -26012,10 +26039,12 @@
         <v>75</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>597</v>
+        <v>113</v>
       </c>
       <c r="L236" s="2"/>
-      <c r="M236" s="2"/>
+      <c r="M236" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
@@ -26023,7 +26052,7 @@
       </c>
       <c r="Q236" s="2"/>
       <c r="R236" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S236" t="s" s="2">
         <v>75</v>
@@ -26065,26 +26094,525 @@
         <v>75</v>
       </c>
       <c r="AF236" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG236" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH236" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI236" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ236" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK236" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="237" hidden="true">
+      <c r="A237" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C237" s="2"/>
+      <c r="D237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E237" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="F237" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G237" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K237" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L237" s="2"/>
+      <c r="M237" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N237" s="2"/>
+      <c r="O237" s="2"/>
+      <c r="P237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q237" s="2"/>
+      <c r="R237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF237" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG237" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH237" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ237" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK237" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="238" hidden="true">
+      <c r="A238" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C238" s="2"/>
+      <c r="D238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E238" s="2"/>
+      <c r="F238" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K238" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L238" s="2"/>
+      <c r="M238" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N238" s="2"/>
+      <c r="O238" s="2"/>
+      <c r="P238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q238" s="2"/>
+      <c r="R238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF238" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG238" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ238" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK238" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="239" hidden="true">
+      <c r="A239" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AG236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH236" t="s" s="2">
+      <c r="B239" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C239" s="2"/>
+      <c r="D239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E239" s="2"/>
+      <c r="F239" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G239" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K239" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L239" s="2"/>
+      <c r="M239" s="2"/>
+      <c r="N239" s="2"/>
+      <c r="O239" s="2"/>
+      <c r="P239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q239" s="2"/>
+      <c r="R239" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="S239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X239" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="Y239" s="2"/>
+      <c r="Z239" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AA239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF239" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG239" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH239" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ239" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK239" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="240" hidden="true">
+      <c r="A240" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C240" s="2"/>
+      <c r="D240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E240" s="2"/>
+      <c r="F240" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G240" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K240" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="L240" s="2"/>
+      <c r="M240" s="2"/>
+      <c r="N240" s="2"/>
+      <c r="O240" s="2"/>
+      <c r="P240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q240" s="2"/>
+      <c r="R240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF240" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AG240" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH240" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK240" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="241" hidden="true">
+      <c r="A241" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C241" s="2"/>
+      <c r="D241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E241" s="2"/>
+      <c r="F241" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G241" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AI236" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ236" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK236" t="s" s="2">
+      <c r="H241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K241" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L241" s="2"/>
+      <c r="M241" s="2"/>
+      <c r="N241" s="2"/>
+      <c r="O241" s="2"/>
+      <c r="P241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q241" s="2"/>
+      <c r="R241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF241" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG241" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH241" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ241" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK241" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK236">
+  <autoFilter ref="A1:AK241">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -26094,7 +26622,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI235">
+  <conditionalFormatting sqref="A2:AI240">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$240</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7525" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7493" uniqueCount="596">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1055,6 +1055,21 @@
     <t>templateId est optionnel. S'il est présent, son root peut être 1.2.250.1.213.1.1.3.109 et/ou une autre OID valide</t>
   </si>
   <si>
+    <t>Observation.participant.templateId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.participant.templateId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Observation.participant.templateId.displayable</t>
+  </si>
+  <si>
+    <t>Observation.participant.templateId.root</t>
+  </si>
+  <si>
+    <t>Observation.participant.templateId.extension</t>
+  </si>
+  <si>
     <t>Observation.participant.templateId:templateId</t>
   </si>
   <si>
@@ -1067,61 +1082,25 @@
     <t>Observation.participant.templateId:templateId.nullFlavor</t>
   </si>
   <si>
-    <t>Observation.participant.templateId.nullFlavor</t>
-  </si>
-  <si>
     <t>Observation.participant.templateId:templateId.assigningAuthorityName</t>
   </si>
   <si>
-    <t>Observation.participant.templateId.assigningAuthorityName</t>
-  </si>
-  <si>
     <t>Observation.participant.templateId:templateId.displayable</t>
   </si>
   <si>
-    <t>Observation.participant.templateId.displayable</t>
-  </si>
-  <si>
     <t>Observation.participant.templateId:templateId.root</t>
   </si>
   <si>
-    <t>Observation.participant.templateId.root</t>
-  </si>
-  <si>
     <t>1.2.250.1.213.1.1.3.109</t>
   </si>
   <si>
     <t>Observation.participant.templateId:templateId.extension</t>
   </si>
   <si>
-    <t>Observation.participant.templateId.extension</t>
-  </si>
-  <si>
-    <t>Observation.participant.templateId:templateId-other</t>
-  </si>
-  <si>
-    <t>templateId-other</t>
-  </si>
-  <si>
-    <t>Autre TemplateId</t>
-  </si>
-  <si>
-    <t>Observation.participant.templateId:templateId-other.nullFlavor</t>
-  </si>
-  <si>
-    <t>Observation.participant.templateId:templateId-other.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Observation.participant.templateId:templateId-other.displayable</t>
-  </si>
-  <si>
-    <t>Observation.participant.templateId:templateId-other.root</t>
-  </si>
-  <si>
-    <t>Observation.participant.templateId:templateId-other.extension</t>
-  </si>
-  <si>
     <t>Observation.participant.typeCode</t>
+  </si>
+  <si>
+    <t>Code issu du JDV_HL7_v3_ParticipationType_CISIS (2.16.840.1.113883.1.11.10901).</t>
   </si>
   <si>
     <t>RESP</t>
@@ -1277,8 +1256,8 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
+    <t>profile:observation}
+profile:act}</t>
   </si>
   <si>
     <t>Observation.entryRelationship:frEvaluationComposant</t>
@@ -2195,7 +2174,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK241"/>
+  <dimension ref="A1:AK240"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.15234375" customWidth="true" bestFit="true"/>
@@ -12336,15 +12315,15 @@
         <v>337</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F100" t="s" s="2">
         <v>81</v>
       </c>
@@ -12361,13 +12340,11 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>339</v>
+        <v>87</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -12394,13 +12371,11 @@
         <v>75</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>75</v>
@@ -12418,13 +12393,13 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>75</v>
@@ -12438,17 +12413,17 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>81</v>
@@ -12466,11 +12441,11 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12497,11 +12472,13 @@
         <v>75</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>75</v>
@@ -12519,7 +12496,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -12539,17 +12516,17 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F102" t="s" s="2">
         <v>81</v>
@@ -12567,11 +12544,11 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -12622,7 +12599,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -12642,20 +12619,20 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>76</v>
@@ -12670,11 +12647,11 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" t="s" s="2">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12725,7 +12702,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12745,20 +12722,20 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>76</v>
@@ -12773,11 +12750,11 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12789,7 +12766,7 @@
         <v>75</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>348</v>
+        <v>75</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>75</v>
@@ -12828,7 +12805,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -12848,18 +12825,18 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C105" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="D105" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E105" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>81</v>
       </c>
@@ -12876,11 +12853,13 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L105" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="M105" t="s" s="2">
-        <v>119</v>
+        <v>344</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12931,13 +12910,13 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>75</v>
@@ -12951,23 +12930,23 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E106" s="2"/>
+      <c r="E106" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>75</v>
@@ -12979,13 +12958,11 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>353</v>
+        <v>87</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13012,13 +12989,11 @@
         <v>75</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>75</v>
@@ -13036,13 +13011,13 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>75</v>
@@ -13056,17 +13031,17 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>81</v>
@@ -13084,11 +13059,11 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13115,11 +13090,13 @@
         <v>75</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -13137,7 +13114,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -13157,17 +13134,17 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F108" t="s" s="2">
         <v>81</v>
@@ -13185,11 +13162,11 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -13240,7 +13217,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -13260,20 +13237,20 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>76</v>
@@ -13288,11 +13265,11 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" t="s" s="2">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -13304,7 +13281,7 @@
         <v>75</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>75</v>
+        <v>349</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>75</v>
@@ -13343,7 +13320,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -13361,28 +13338,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F110" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>75</v>
@@ -13391,11 +13368,11 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" t="s" s="2">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13446,7 +13423,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -13464,28 +13441,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E111" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>75</v>
@@ -13494,12 +13469,12 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L111" s="2"/>
-      <c r="M111" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -13510,7 +13485,7 @@
         <v>75</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>75</v>
@@ -13525,13 +13500,11 @@
         <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -13549,10 +13522,10 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>120</v>
+        <v>355</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -13567,12 +13540,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13580,13 +13553,13 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>75</v>
@@ -13606,10 +13579,10 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>75</v>
+        <v>357</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>75</v>
@@ -13628,7 +13601,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -13646,10 +13619,10 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>76</v>
@@ -13666,10 +13639,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13692,7 +13665,7 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>86</v>
+        <v>294</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13703,7 +13676,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>364</v>
+        <v>75</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>75</v>
@@ -13721,11 +13694,13 @@
         <v>75</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y113" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z113" t="s" s="2">
-        <v>365</v>
+        <v>75</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>75</v>
@@ -13743,7 +13718,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13761,12 +13736,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13780,7 +13755,7 @@
         <v>76</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>75</v>
@@ -13789,10 +13764,14 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13842,7 +13821,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13860,18 +13839,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F115" t="s" s="2">
         <v>81</v>
       </c>
@@ -13879,7 +13860,7 @@
         <v>76</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>75</v>
@@ -13888,13 +13869,11 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L115" s="2"/>
       <c r="M115" t="s" s="2">
-        <v>370</v>
+        <v>87</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13921,13 +13900,11 @@
         <v>75</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>75</v>
@@ -13945,7 +13922,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>371</v>
+        <v>90</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13965,18 +13942,16 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E116" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>81</v>
       </c>
@@ -13993,11 +13968,11 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>86</v>
+        <v>367</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" t="s" s="2">
-        <v>87</v>
+        <v>368</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14024,11 +13999,13 @@
         <v>75</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y116" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z116" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>75</v>
@@ -14046,7 +14023,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>90</v>
+        <v>369</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -14066,10 +14043,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14092,16 +14069,16 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>374</v>
+        <v>86</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
-        <v>75</v>
+        <v>372</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
@@ -14123,13 +14100,11 @@
         <v>75</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>75</v>
+        <v>373</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>75</v>
@@ -14147,7 +14122,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -14165,18 +14140,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E118" s="2"/>
+      <c r="E118" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="F118" t="s" s="2">
         <v>81</v>
       </c>
@@ -14184,7 +14161,7 @@
         <v>76</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>75</v>
@@ -14193,7 +14170,7 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>86</v>
+        <v>377</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" t="s" s="2">
@@ -14202,7 +14179,7 @@
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
-        <v>379</v>
+        <v>75</v>
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
@@ -14224,59 +14201,61 @@
         <v>75</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y118" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AA118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s" s="2">
-        <v>382</v>
-      </c>
       <c r="B119" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F119" t="s" s="2">
         <v>81</v>
@@ -14285,7 +14264,7 @@
         <v>76</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>75</v>
@@ -14294,11 +14273,11 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14349,7 +14328,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -14369,17 +14348,17 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F120" t="s" s="2">
         <v>81</v>
@@ -14397,11 +14376,11 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14452,7 +14431,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -14470,19 +14449,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F121" t="s" s="2">
         <v>81</v>
@@ -14491,7 +14470,7 @@
         <v>76</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>75</v>
@@ -14500,11 +14479,11 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -14555,7 +14534,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -14573,20 +14552,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E122" t="s" s="2">
-        <v>398</v>
-      </c>
+      <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>81</v>
       </c>
@@ -14594,7 +14571,7 @@
         <v>76</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>75</v>
@@ -14603,12 +14580,10 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>384</v>
+        <v>294</v>
       </c>
       <c r="L122" s="2"/>
-      <c r="M122" t="s" s="2">
-        <v>399</v>
-      </c>
+      <c r="M122" s="2"/>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14658,7 +14633,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -14676,12 +14651,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14689,13 +14664,13 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>75</v>
@@ -14704,10 +14679,14 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L123" s="2"/>
-      <c r="M123" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -14757,10 +14736,10 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>76</v>
@@ -14775,12 +14754,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14788,10 +14767,10 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>170</v>
@@ -14803,14 +14782,10 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="L124" s="2"/>
+      <c r="M124" s="2"/>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -14848,25 +14823,23 @@
         <v>75</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="AC124" s="2"/>
       <c r="AD124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>75</v>
@@ -14880,12 +14853,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C125" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="D125" t="s" s="2">
         <v>75</v>
       </c>
@@ -14897,7 +14872,7 @@
         <v>82</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
@@ -14906,7 +14881,7 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14947,17 +14922,19 @@
         <v>75</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AC125" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -14977,23 +14954,23 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C126" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E126" s="2"/>
+      <c r="E126" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>75</v>
@@ -15005,10 +14982,12 @@
         <v>75</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>408</v>
+        <v>86</v>
       </c>
       <c r="L126" s="2"/>
-      <c r="M126" s="2"/>
+      <c r="M126" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -15034,13 +15013,11 @@
         <v>75</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>75</v>
@@ -15058,13 +15035,13 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>407</v>
+        <v>90</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>75</v>
@@ -15078,23 +15055,21 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E127" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>75</v>
@@ -15106,11 +15081,11 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -15137,11 +15112,13 @@
         <v>75</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y127" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z127" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>75</v>
@@ -15159,13 +15136,13 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>75</v>
@@ -15179,10 +15156,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15193,7 +15170,7 @@
         <v>81</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>75</v>
@@ -15205,11 +15182,11 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -15260,19 +15237,19 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>75</v>
@@ -15280,16 +15257,18 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E129" s="2"/>
+      <c r="E129" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F129" t="s" s="2">
         <v>81</v>
       </c>
@@ -15306,11 +15285,11 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -15337,13 +15316,11 @@
         <v>75</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>75</v>
@@ -15361,7 +15338,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -15373,7 +15350,7 @@
         <v>75</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>75</v>
@@ -15381,17 +15358,17 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F130" t="s" s="2">
         <v>81</v>
@@ -15409,11 +15386,11 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15440,11 +15417,13 @@
         <v>75</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y130" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z130" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>75</v>
@@ -15462,7 +15441,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -15482,17 +15461,17 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F131" t="s" s="2">
         <v>81</v>
@@ -15510,11 +15489,11 @@
         <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -15565,7 +15544,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -15585,20 +15564,20 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F132" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>76</v>
@@ -15613,11 +15592,11 @@
         <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -15626,7 +15605,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>75</v>
@@ -15668,7 +15647,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15688,17 +15667,17 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F133" t="s" s="2">
         <v>76</v>
@@ -15716,11 +15695,11 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15729,7 +15708,7 @@
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S133" t="s" s="2">
         <v>75</v>
@@ -15771,7 +15750,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -15791,23 +15770,21 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E134" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>75</v>
@@ -15819,11 +15796,11 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15874,13 +15851,13 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>75</v>
@@ -15894,10 +15871,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15905,10 +15882,10 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>75</v>
@@ -15920,12 +15897,10 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L135" s="2"/>
-      <c r="M135" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M135" s="2"/>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -15936,7 +15911,7 @@
         <v>75</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>75</v>
+        <v>425</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>75</v>
@@ -15951,13 +15926,11 @@
         <v>75</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>75</v>
+        <v>426</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>75</v>
@@ -15975,13 +15948,13 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>126</v>
+        <v>427</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>75</v>
@@ -15995,10 +15968,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16006,7 +15979,7 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>76</v>
@@ -16021,10 +15994,12 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L136" s="2"/>
-      <c r="M136" s="2"/>
+      <c r="M136" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -16035,7 +16010,7 @@
         <v>75</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>432</v>
+        <v>34</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>75</v>
@@ -16050,11 +16025,13 @@
         <v>75</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y136" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z136" t="s" s="2">
-        <v>433</v>
+        <v>75</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>75</v>
@@ -16072,10 +16049,10 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>76</v>
@@ -16092,10 +16069,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16122,19 +16099,19 @@
       </c>
       <c r="L137" s="2"/>
       <c r="M137" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>75</v>
@@ -16173,7 +16150,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -16193,10 +16170,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16222,13 +16199,11 @@
         <v>108</v>
       </c>
       <c r="L138" s="2"/>
-      <c r="M138" t="s" s="2">
-        <v>441</v>
-      </c>
+      <c r="M138" s="2"/>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
-        <v>442</v>
+        <v>75</v>
       </c>
       <c r="Q138" s="2"/>
       <c r="R138" t="s" s="2">
@@ -16274,7 +16249,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -16294,10 +16269,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16320,7 +16295,7 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>108</v>
+        <v>442</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -16373,7 +16348,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -16393,10 +16368,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16419,7 +16394,7 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16472,7 +16447,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -16492,10 +16467,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16506,7 +16481,7 @@
         <v>81</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>75</v>
@@ -16518,7 +16493,7 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16571,7 +16546,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -16591,10 +16566,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16617,7 +16592,7 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16670,7 +16645,7 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -16690,10 +16665,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16716,7 +16691,7 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16769,7 +16744,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -16789,10 +16764,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16815,7 +16790,7 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16868,7 +16843,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -16888,10 +16863,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16914,7 +16889,7 @@
         <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16967,7 +16942,7 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -16987,10 +16962,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17013,7 +16988,7 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -17066,7 +17041,7 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -17086,10 +17061,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17112,7 +17087,7 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -17165,7 +17140,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -17185,10 +17160,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17211,7 +17186,7 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -17264,7 +17239,7 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -17284,10 +17259,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17310,7 +17285,7 @@
         <v>75</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
@@ -17363,7 +17338,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -17383,12 +17358,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C150" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="D150" t="s" s="2">
         <v>75</v>
       </c>
@@ -17409,9 +17386,11 @@
         <v>75</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="L150" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -17462,13 +17441,13 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>75</v>
@@ -17482,18 +17461,18 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E151" s="2"/>
+      <c r="E151" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F151" t="s" s="2">
         <v>81</v>
       </c>
@@ -17510,12 +17489,12 @@
         <v>75</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M151" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="L151" s="2"/>
+      <c r="M151" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -17541,13 +17520,11 @@
         <v>75</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>75</v>
@@ -17565,13 +17542,13 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>407</v>
+        <v>90</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>75</v>
@@ -17585,23 +17562,21 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E152" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>75</v>
@@ -17613,11 +17588,11 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17644,11 +17619,13 @@
         <v>75</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y152" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z152" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>75</v>
@@ -17666,13 +17643,13 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>75</v>
@@ -17686,10 +17663,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17700,7 +17677,7 @@
         <v>81</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>75</v>
@@ -17712,11 +17689,11 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17767,19 +17744,19 @@
         <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>75</v>
@@ -17787,16 +17764,18 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E154" s="2"/>
+      <c r="E154" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F154" t="s" s="2">
         <v>81</v>
       </c>
@@ -17813,11 +17792,11 @@
         <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -17844,13 +17823,11 @@
         <v>75</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>75</v>
@@ -17868,7 +17845,7 @@
         <v>75</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -17880,7 +17857,7 @@
         <v>75</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>75</v>
@@ -17888,17 +17865,17 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F155" t="s" s="2">
         <v>81</v>
@@ -17916,11 +17893,11 @@
         <v>75</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -17947,11 +17924,13 @@
         <v>75</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y155" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z155" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>75</v>
@@ -17969,7 +17948,7 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -17989,17 +17968,17 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F156" t="s" s="2">
         <v>81</v>
@@ -18017,11 +17996,11 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -18072,7 +18051,7 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -18092,20 +18071,20 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F157" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G157" t="s" s="2">
         <v>76</v>
@@ -18120,11 +18099,11 @@
         <v>75</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -18133,7 +18112,7 @@
       </c>
       <c r="Q157" s="2"/>
       <c r="R157" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S157" t="s" s="2">
         <v>75</v>
@@ -18175,7 +18154,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -18195,17 +18174,17 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F158" t="s" s="2">
         <v>76</v>
@@ -18223,11 +18202,11 @@
         <v>75</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -18236,7 +18215,7 @@
       </c>
       <c r="Q158" s="2"/>
       <c r="R158" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S158" t="s" s="2">
         <v>75</v>
@@ -18278,7 +18257,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -18298,23 +18277,21 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E159" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>75</v>
@@ -18326,11 +18303,11 @@
         <v>75</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -18381,13 +18358,13 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>75</v>
@@ -18401,10 +18378,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18412,10 +18389,10 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>75</v>
@@ -18427,12 +18404,10 @@
         <v>75</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L160" s="2"/>
-      <c r="M160" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M160" s="2"/>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -18443,7 +18418,7 @@
         <v>75</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>75</v>
+        <v>425</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>75</v>
@@ -18458,13 +18433,11 @@
         <v>75</v>
       </c>
       <c r="X160" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y160" s="2"/>
       <c r="Z160" t="s" s="2">
-        <v>75</v>
+        <v>426</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>75</v>
@@ -18482,13 +18455,13 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>126</v>
+        <v>427</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>75</v>
@@ -18502,10 +18475,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18513,7 +18486,7 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>76</v>
@@ -18528,10 +18501,12 @@
         <v>75</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L161" s="2"/>
-      <c r="M161" s="2"/>
+      <c r="M161" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -18542,7 +18517,7 @@
         <v>75</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>432</v>
+        <v>34</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>75</v>
@@ -18557,11 +18532,13 @@
         <v>75</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y161" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z161" t="s" s="2">
-        <v>433</v>
+        <v>75</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>75</v>
@@ -18579,10 +18556,10 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>76</v>
@@ -18599,10 +18576,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18629,19 +18606,19 @@
       </c>
       <c r="L162" s="2"/>
       <c r="M162" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="Q162" s="2"/>
       <c r="R162" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>75</v>
@@ -18680,7 +18657,7 @@
         <v>75</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -18700,10 +18677,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18729,13 +18706,11 @@
         <v>108</v>
       </c>
       <c r="L163" s="2"/>
-      <c r="M163" t="s" s="2">
-        <v>441</v>
-      </c>
+      <c r="M163" s="2"/>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
-        <v>442</v>
+        <v>75</v>
       </c>
       <c r="Q163" s="2"/>
       <c r="R163" t="s" s="2">
@@ -18781,7 +18756,7 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -18801,10 +18776,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18827,7 +18802,7 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>108</v>
+        <v>442</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18880,7 +18855,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -18900,10 +18875,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18926,7 +18901,7 @@
         <v>75</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18979,7 +18954,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -18999,10 +18974,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19013,7 +18988,7 @@
         <v>81</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>75</v>
@@ -19025,7 +19000,7 @@
         <v>75</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -19078,7 +19053,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -19098,10 +19073,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19124,7 +19099,7 @@
         <v>75</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -19177,7 +19152,7 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -19197,10 +19172,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19223,7 +19198,7 @@
         <v>75</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>461</v>
+        <v>505</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -19276,7 +19251,7 @@
         <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -19296,10 +19271,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19322,7 +19297,7 @@
         <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>512</v>
+        <v>462</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -19375,7 +19350,7 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -19395,10 +19370,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19421,7 +19396,7 @@
         <v>75</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19474,7 +19449,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19494,10 +19469,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19520,7 +19495,7 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19573,7 +19548,7 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -19593,10 +19568,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19619,7 +19594,7 @@
         <v>75</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -19672,7 +19647,7 @@
         <v>75</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -19692,10 +19667,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19718,7 +19693,7 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -19771,7 +19746,7 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -19791,10 +19766,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19817,7 +19792,7 @@
         <v>75</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -19870,7 +19845,7 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -19890,12 +19865,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C175" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="C175" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="D175" t="s" s="2">
         <v>75</v>
       </c>
@@ -19904,7 +19881,7 @@
         <v>81</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>75</v>
@@ -19916,9 +19893,11 @@
         <v>75</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="L175" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -19969,13 +19948,13 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>75</v>
@@ -19989,23 +19968,23 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E176" s="2"/>
+      <c r="E176" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>75</v>
@@ -20017,12 +19996,12 @@
         <v>75</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="L176" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="M176" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="L176" s="2"/>
+      <c r="M176" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -20048,13 +20027,11 @@
         <v>75</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y176" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>75</v>
@@ -20072,13 +20049,13 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>407</v>
+        <v>90</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>75</v>
@@ -20092,23 +20069,21 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E177" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>75</v>
@@ -20120,11 +20095,11 @@
         <v>75</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -20151,11 +20126,13 @@
         <v>75</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y177" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y177" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z177" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>75</v>
@@ -20173,13 +20150,13 @@
         <v>75</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>75</v>
@@ -20193,10 +20170,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20207,7 +20184,7 @@
         <v>81</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>75</v>
@@ -20219,11 +20196,11 @@
         <v>75</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -20274,19 +20251,19 @@
         <v>75</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>75</v>
@@ -20294,16 +20271,18 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E179" s="2"/>
+      <c r="E179" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F179" t="s" s="2">
         <v>81</v>
       </c>
@@ -20320,11 +20299,11 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -20351,13 +20330,11 @@
         <v>75</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>75</v>
@@ -20375,7 +20352,7 @@
         <v>75</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -20387,7 +20364,7 @@
         <v>75</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>75</v>
@@ -20395,17 +20372,17 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E180" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F180" t="s" s="2">
         <v>81</v>
@@ -20423,11 +20400,11 @@
         <v>75</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -20454,11 +20431,13 @@
         <v>75</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y180" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z180" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>75</v>
@@ -20476,7 +20455,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -20496,17 +20475,17 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E181" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F181" t="s" s="2">
         <v>81</v>
@@ -20524,11 +20503,11 @@
         <v>75</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L181" s="2"/>
       <c r="M181" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -20579,7 +20558,7 @@
         <v>75</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -20599,20 +20578,20 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F182" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G182" t="s" s="2">
         <v>76</v>
@@ -20627,11 +20606,11 @@
         <v>75</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L182" s="2"/>
       <c r="M182" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -20640,7 +20619,7 @@
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>75</v>
@@ -20682,7 +20661,7 @@
         <v>75</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -20702,17 +20681,17 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F183" t="s" s="2">
         <v>76</v>
@@ -20730,11 +20709,11 @@
         <v>75</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -20743,7 +20722,7 @@
       </c>
       <c r="Q183" s="2"/>
       <c r="R183" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S183" t="s" s="2">
         <v>75</v>
@@ -20785,7 +20764,7 @@
         <v>75</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -20805,23 +20784,21 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E184" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>75</v>
@@ -20833,11 +20810,11 @@
         <v>75</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L184" s="2"/>
       <c r="M184" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -20888,13 +20865,13 @@
         <v>75</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>75</v>
@@ -20908,10 +20885,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20919,10 +20896,10 @@
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>75</v>
@@ -20934,12 +20911,10 @@
         <v>75</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L185" s="2"/>
-      <c r="M185" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M185" s="2"/>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -20950,7 +20925,7 @@
         <v>75</v>
       </c>
       <c r="S185" t="s" s="2">
-        <v>75</v>
+        <v>525</v>
       </c>
       <c r="T185" t="s" s="2">
         <v>75</v>
@@ -20965,13 +20940,11 @@
         <v>75</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y185" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y185" s="2"/>
       <c r="Z185" t="s" s="2">
-        <v>75</v>
+        <v>426</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>75</v>
@@ -20989,13 +20962,13 @@
         <v>75</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>126</v>
+        <v>427</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI185" t="s" s="2">
         <v>75</v>
@@ -21009,10 +20982,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21020,7 +20993,7 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G186" t="s" s="2">
         <v>76</v>
@@ -21035,10 +21008,12 @@
         <v>75</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L186" s="2"/>
-      <c r="M186" s="2"/>
+      <c r="M186" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -21049,7 +21024,7 @@
         <v>75</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>532</v>
+        <v>435</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>75</v>
@@ -21064,11 +21039,13 @@
         <v>75</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y186" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z186" t="s" s="2">
-        <v>433</v>
+        <v>75</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>75</v>
@@ -21086,10 +21063,10 @@
         <v>75</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>76</v>
@@ -21106,10 +21083,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21136,19 +21113,19 @@
       </c>
       <c r="L187" s="2"/>
       <c r="M187" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="Q187" s="2"/>
       <c r="R187" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S187" t="s" s="2">
-        <v>442</v>
+        <v>75</v>
       </c>
       <c r="T187" t="s" s="2">
         <v>75</v>
@@ -21187,7 +21164,7 @@
         <v>75</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -21207,10 +21184,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21236,13 +21213,11 @@
         <v>108</v>
       </c>
       <c r="L188" s="2"/>
-      <c r="M188" t="s" s="2">
-        <v>441</v>
-      </c>
+      <c r="M188" s="2"/>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
-        <v>442</v>
+        <v>75</v>
       </c>
       <c r="Q188" s="2"/>
       <c r="R188" t="s" s="2">
@@ -21288,7 +21263,7 @@
         <v>75</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -21308,10 +21283,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21334,7 +21309,7 @@
         <v>75</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>108</v>
+        <v>442</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -21387,7 +21362,7 @@
         <v>75</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -21407,10 +21382,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21433,7 +21408,7 @@
         <v>75</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
@@ -21486,7 +21461,7 @@
         <v>75</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -21506,10 +21481,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21532,7 +21507,7 @@
         <v>75</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>453</v>
+        <v>532</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
@@ -21585,7 +21560,7 @@
         <v>75</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -21605,10 +21580,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21631,7 +21606,7 @@
         <v>75</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>539</v>
+        <v>454</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -21684,7 +21659,7 @@
         <v>75</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -21704,10 +21679,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21718,7 +21693,7 @@
         <v>81</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>75</v>
@@ -21730,7 +21705,7 @@
         <v>75</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>461</v>
+        <v>535</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
@@ -21783,7 +21758,7 @@
         <v>75</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -21803,10 +21778,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21829,7 +21804,7 @@
         <v>75</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>542</v>
+        <v>462</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -21882,7 +21857,7 @@
         <v>75</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -21902,10 +21877,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21928,7 +21903,7 @@
         <v>75</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -21981,7 +21956,7 @@
         <v>75</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -22001,10 +21976,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22027,7 +22002,7 @@
         <v>75</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -22080,7 +22055,7 @@
         <v>75</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
@@ -22100,10 +22075,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22126,7 +22101,7 @@
         <v>75</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -22179,7 +22154,7 @@
         <v>75</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -22199,10 +22174,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22225,7 +22200,7 @@
         <v>75</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22278,7 +22253,7 @@
         <v>75</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -22298,10 +22273,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22324,7 +22299,7 @@
         <v>75</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22377,7 +22352,7 @@
         <v>75</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -22397,12 +22372,14 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C200" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="D200" t="s" s="2">
         <v>75</v>
       </c>
@@ -22411,7 +22388,7 @@
         <v>81</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>75</v>
@@ -22423,9 +22400,11 @@
         <v>75</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="L200" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="L200" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -22476,13 +22455,13 @@
         <v>75</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI200" t="s" s="2">
         <v>75</v>
@@ -22496,23 +22475,23 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C201" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E201" s="2"/>
+      <c r="E201" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F201" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H201" t="s" s="2">
         <v>75</v>
@@ -22524,12 +22503,12 @@
         <v>75</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="L201" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="M201" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="L201" s="2"/>
+      <c r="M201" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -22555,13 +22534,11 @@
         <v>75</v>
       </c>
       <c r="X201" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y201" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y201" s="2"/>
       <c r="Z201" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>75</v>
@@ -22579,13 +22556,13 @@
         <v>75</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>407</v>
+        <v>90</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI201" t="s" s="2">
         <v>75</v>
@@ -22599,23 +22576,21 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E202" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E202" s="2"/>
       <c r="F202" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H202" t="s" s="2">
         <v>75</v>
@@ -22627,11 +22602,11 @@
         <v>75</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -22658,11 +22633,13 @@
         <v>75</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y202" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y202" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z202" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>75</v>
@@ -22680,13 +22657,13 @@
         <v>75</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>75</v>
@@ -22700,10 +22677,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22714,7 +22691,7 @@
         <v>81</v>
       </c>
       <c r="G203" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H203" t="s" s="2">
         <v>75</v>
@@ -22726,11 +22703,11 @@
         <v>75</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -22781,19 +22758,19 @@
         <v>75</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI203" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>75</v>
@@ -22801,16 +22778,18 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E204" s="2"/>
+      <c r="E204" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F204" t="s" s="2">
         <v>81</v>
       </c>
@@ -22827,11 +22806,11 @@
         <v>75</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -22858,13 +22837,11 @@
         <v>75</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y204" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y204" s="2"/>
       <c r="Z204" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>75</v>
@@ -22882,7 +22859,7 @@
         <v>75</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -22894,7 +22871,7 @@
         <v>75</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>75</v>
@@ -22902,17 +22879,17 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E205" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F205" t="s" s="2">
         <v>81</v>
@@ -22930,11 +22907,11 @@
         <v>75</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -22961,11 +22938,13 @@
         <v>75</v>
       </c>
       <c r="X205" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y205" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y205" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z205" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA205" t="s" s="2">
         <v>75</v>
@@ -22983,7 +22962,7 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -23003,17 +22982,17 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E206" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F206" t="s" s="2">
         <v>81</v>
@@ -23031,11 +23010,11 @@
         <v>75</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L206" s="2"/>
       <c r="M206" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -23086,7 +23065,7 @@
         <v>75</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -23106,20 +23085,20 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E207" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F207" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G207" t="s" s="2">
         <v>76</v>
@@ -23134,11 +23113,11 @@
         <v>75</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L207" s="2"/>
       <c r="M207" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -23147,7 +23126,7 @@
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>75</v>
@@ -23189,7 +23168,7 @@
         <v>75</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -23209,17 +23188,17 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E208" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F208" t="s" s="2">
         <v>76</v>
@@ -23237,11 +23216,11 @@
         <v>75</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L208" s="2"/>
       <c r="M208" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -23250,7 +23229,7 @@
       </c>
       <c r="Q208" s="2"/>
       <c r="R208" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S208" t="s" s="2">
         <v>75</v>
@@ -23292,7 +23271,7 @@
         <v>75</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -23312,23 +23291,21 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E209" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>75</v>
@@ -23340,11 +23317,11 @@
         <v>75</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L209" s="2"/>
       <c r="M209" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -23395,13 +23372,13 @@
         <v>75</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>75</v>
@@ -23415,10 +23392,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23426,10 +23403,10 @@
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>75</v>
@@ -23441,12 +23418,10 @@
         <v>75</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L210" s="2"/>
-      <c r="M210" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M210" s="2"/>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -23457,7 +23432,7 @@
         <v>75</v>
       </c>
       <c r="S210" t="s" s="2">
-        <v>75</v>
+        <v>555</v>
       </c>
       <c r="T210" t="s" s="2">
         <v>75</v>
@@ -23472,13 +23447,11 @@
         <v>75</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y210" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y210" s="2"/>
       <c r="Z210" t="s" s="2">
-        <v>75</v>
+        <v>426</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>75</v>
@@ -23496,13 +23469,13 @@
         <v>75</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>126</v>
+        <v>427</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>75</v>
@@ -23516,10 +23489,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23527,7 +23500,7 @@
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G211" t="s" s="2">
         <v>76</v>
@@ -23542,10 +23515,12 @@
         <v>75</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L211" s="2"/>
-      <c r="M211" s="2"/>
+      <c r="M211" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -23556,7 +23531,7 @@
         <v>75</v>
       </c>
       <c r="S211" t="s" s="2">
-        <v>562</v>
+        <v>34</v>
       </c>
       <c r="T211" t="s" s="2">
         <v>75</v>
@@ -23571,11 +23546,13 @@
         <v>75</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y211" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y211" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z211" t="s" s="2">
-        <v>433</v>
+        <v>75</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>75</v>
@@ -23593,10 +23570,10 @@
         <v>75</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH211" t="s" s="2">
         <v>76</v>
@@ -23613,10 +23590,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23643,19 +23620,19 @@
       </c>
       <c r="L212" s="2"/>
       <c r="M212" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="Q212" s="2"/>
       <c r="R212" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S212" t="s" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="T212" t="s" s="2">
         <v>75</v>
@@ -23694,7 +23671,7 @@
         <v>75</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
@@ -23714,10 +23691,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23743,13 +23720,11 @@
         <v>108</v>
       </c>
       <c r="L213" s="2"/>
-      <c r="M213" t="s" s="2">
-        <v>441</v>
-      </c>
+      <c r="M213" s="2"/>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
-        <v>442</v>
+        <v>75</v>
       </c>
       <c r="Q213" s="2"/>
       <c r="R213" t="s" s="2">
@@ -23795,7 +23770,7 @@
         <v>75</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -23815,10 +23790,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23841,7 +23816,7 @@
         <v>75</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>108</v>
+        <v>442</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -23894,7 +23869,7 @@
         <v>75</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -23914,10 +23889,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -23940,7 +23915,7 @@
         <v>75</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
@@ -23993,7 +23968,7 @@
         <v>75</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -24013,10 +23988,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24039,7 +24014,7 @@
         <v>75</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>453</v>
+        <v>562</v>
       </c>
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
@@ -24092,7 +24067,7 @@
         <v>75</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -24112,10 +24087,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24138,7 +24113,7 @@
         <v>75</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>569</v>
+        <v>454</v>
       </c>
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
@@ -24191,7 +24166,7 @@
         <v>75</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -24211,10 +24186,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24225,7 +24200,7 @@
         <v>81</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>75</v>
@@ -24237,7 +24212,7 @@
         <v>75</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>461</v>
+        <v>535</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
@@ -24290,7 +24265,7 @@
         <v>75</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -24310,10 +24285,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24336,7 +24311,7 @@
         <v>75</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>542</v>
+        <v>462</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -24389,7 +24364,7 @@
         <v>75</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -24409,10 +24384,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24435,7 +24410,7 @@
         <v>75</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24488,7 +24463,7 @@
         <v>75</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -24508,10 +24483,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24534,7 +24509,7 @@
         <v>75</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24587,7 +24562,7 @@
         <v>75</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -24607,10 +24582,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24633,7 +24608,7 @@
         <v>75</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24686,7 +24661,7 @@
         <v>75</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -24706,10 +24681,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24732,7 +24707,7 @@
         <v>75</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24785,7 +24760,7 @@
         <v>75</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -24805,10 +24780,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24831,7 +24806,7 @@
         <v>75</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -24884,7 +24859,7 @@
         <v>75</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -24904,10 +24879,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>488</v>
+        <v>571</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -24918,7 +24893,7 @@
         <v>81</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>75</v>
@@ -24930,7 +24905,7 @@
         <v>75</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>489</v>
+        <v>572</v>
       </c>
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
@@ -24983,13 +24958,13 @@
         <v>75</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>490</v>
+        <v>571</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI225" t="s" s="2">
         <v>75</v>
@@ -25003,10 +24978,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25029,7 +25004,7 @@
         <v>75</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
@@ -25082,7 +25057,7 @@
         <v>75</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -25102,10 +25077,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25128,7 +25103,7 @@
         <v>75</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -25181,7 +25156,7 @@
         <v>75</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -25201,10 +25176,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25227,10 +25202,12 @@
         <v>75</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="L228" s="2"/>
-      <c r="M228" s="2"/>
+      <c r="M228" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
@@ -25280,7 +25257,7 @@
         <v>75</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -25300,21 +25277,23 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E229" s="2"/>
+      <c r="E229" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>75</v>
@@ -25326,11 +25305,11 @@
         <v>75</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>585</v>
+        <v>86</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" t="s" s="2">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -25357,13 +25336,11 @@
         <v>75</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y229" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y229" s="2"/>
       <c r="Z229" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>75</v>
@@ -25381,13 +25358,13 @@
         <v>75</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>584</v>
+        <v>90</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>75</v>
@@ -25401,23 +25378,21 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E230" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>75</v>
@@ -25429,11 +25404,11 @@
         <v>75</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L230" s="2"/>
       <c r="M230" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -25460,11 +25435,13 @@
         <v>75</v>
       </c>
       <c r="X230" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y230" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y230" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z230" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>75</v>
@@ -25482,13 +25459,13 @@
         <v>75</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>75</v>
@@ -25502,10 +25479,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25516,7 +25493,7 @@
         <v>81</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>75</v>
@@ -25528,11 +25505,11 @@
         <v>75</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -25583,19 +25560,19 @@
         <v>75</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI231" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK231" t="s" s="2">
         <v>75</v>
@@ -25603,16 +25580,18 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E232" s="2"/>
+      <c r="E232" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F232" t="s" s="2">
         <v>81</v>
       </c>
@@ -25629,11 +25608,11 @@
         <v>75</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L232" s="2"/>
       <c r="M232" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -25660,13 +25639,11 @@
         <v>75</v>
       </c>
       <c r="X232" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y232" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y232" s="2"/>
       <c r="Z232" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>75</v>
@@ -25684,7 +25661,7 @@
         <v>75</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -25696,7 +25673,7 @@
         <v>75</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK232" t="s" s="2">
         <v>75</v>
@@ -25704,17 +25681,17 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E233" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F233" t="s" s="2">
         <v>81</v>
@@ -25732,11 +25709,11 @@
         <v>75</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L233" s="2"/>
       <c r="M233" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -25763,11 +25740,13 @@
         <v>75</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y233" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y233" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z233" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>75</v>
@@ -25785,7 +25764,7 @@
         <v>75</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -25805,17 +25784,17 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E234" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F234" t="s" s="2">
         <v>81</v>
@@ -25833,11 +25812,11 @@
         <v>75</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L234" s="2"/>
       <c r="M234" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -25888,7 +25867,7 @@
         <v>75</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
@@ -25908,20 +25887,20 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E235" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F235" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G235" t="s" s="2">
         <v>76</v>
@@ -25936,11 +25915,11 @@
         <v>75</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L235" s="2"/>
       <c r="M235" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -25949,7 +25928,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>75</v>
@@ -25991,7 +25970,7 @@
         <v>75</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -26011,17 +25990,17 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E236" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F236" t="s" s="2">
         <v>76</v>
@@ -26039,11 +26018,11 @@
         <v>75</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L236" s="2"/>
       <c r="M236" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -26052,7 +26031,7 @@
       </c>
       <c r="Q236" s="2"/>
       <c r="R236" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S236" t="s" s="2">
         <v>75</v>
@@ -26094,7 +26073,7 @@
         <v>75</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
@@ -26114,23 +26093,21 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E237" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>75</v>
@@ -26142,11 +26119,11 @@
         <v>75</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L237" s="2"/>
       <c r="M237" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -26197,13 +26174,13 @@
         <v>75</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI237" t="s" s="2">
         <v>75</v>
@@ -26217,10 +26194,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26231,7 +26208,7 @@
         <v>81</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>75</v>
@@ -26243,12 +26220,10 @@
         <v>75</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L238" s="2"/>
-      <c r="M238" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M238" s="2"/>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
@@ -26256,7 +26231,7 @@
       </c>
       <c r="Q238" s="2"/>
       <c r="R238" t="s" s="2">
-        <v>75</v>
+        <v>590</v>
       </c>
       <c r="S238" t="s" s="2">
         <v>75</v>
@@ -26274,13 +26249,11 @@
         <v>75</v>
       </c>
       <c r="X238" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y238" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y238" s="2"/>
       <c r="Z238" t="s" s="2">
-        <v>75</v>
+        <v>591</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>75</v>
@@ -26298,13 +26271,13 @@
         <v>75</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>126</v>
+        <v>589</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI238" t="s" s="2">
         <v>75</v>
@@ -26318,10 +26291,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26329,7 +26302,7 @@
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G239" t="s" s="2">
         <v>76</v>
@@ -26344,7 +26317,7 @@
         <v>75</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>86</v>
+        <v>593</v>
       </c>
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
@@ -26355,7 +26328,7 @@
       </c>
       <c r="Q239" s="2"/>
       <c r="R239" t="s" s="2">
-        <v>597</v>
+        <v>75</v>
       </c>
       <c r="S239" t="s" s="2">
         <v>75</v>
@@ -26373,11 +26346,13 @@
         <v>75</v>
       </c>
       <c r="X239" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y239" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y239" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z239" t="s" s="2">
-        <v>598</v>
+        <v>75</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>75</v>
@@ -26395,10 +26370,10 @@
         <v>75</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AG239" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH239" t="s" s="2">
         <v>76</v>
@@ -26415,10 +26390,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26426,10 +26401,10 @@
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H240" t="s" s="2">
         <v>75</v>
@@ -26441,7 +26416,7 @@
         <v>75</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
@@ -26494,13 +26469,13 @@
         <v>75</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="AG240" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH240" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI240" t="s" s="2">
         <v>75</v>
@@ -26509,110 +26484,11 @@
         <v>75</v>
       </c>
       <c r="AK240" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="241" hidden="true">
-      <c r="A241" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C241" s="2"/>
-      <c r="D241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E241" s="2"/>
-      <c r="F241" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G241" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K241" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="L241" s="2"/>
-      <c r="M241" s="2"/>
-      <c r="N241" s="2"/>
-      <c r="O241" s="2"/>
-      <c r="P241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q241" s="2"/>
-      <c r="R241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF241" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AG241" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH241" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ241" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK241" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK241">
+  <autoFilter ref="A1:AK240">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -26622,7 +26498,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI240">
+  <conditionalFormatting sqref="A2:AI239">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -13250,7 +13250,7 @@
         <v>112</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>76</v>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
